--- a/berichte/Report v3_1.xlsx
+++ b/berichte/Report v3_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oniku\IdeaProjects\SPM_MoinMetrics\berichte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AC93F8D-A16F-49A3-9251-4747E1FB2076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F69E9B3-ADC2-4D13-BB30-50336D16483A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,17 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="93">
-  <si>
-    <t>Hier kommen die Risiken, Bedenken und Sorgen; Sachen die nicht so super gelaufen sind. Punkte aus dem vorherigen Berichtszeitraum werden hier wiederholt wenn sie bis jetzt nicht vom Tisch sind. 
-Bitte nicht nur die Probleme erwähnen sondern auch mögliche Lösungen.</t>
-  </si>
-  <si>
-    <t>Hier kommen die sonstigen Mitteilungen. Hier kommen die sonstigen Mitteilungen. Hier kommen die sonstigen Mitteilungen.</t>
-  </si>
-  <si>
-    <t>Hier kommen die Ziele für den nächsten Zeitraum. Hier kommen die Ziele für den nächsten Zeitraum. Hier kommen die Ziele für den nächsten Zeitraum.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
   <si>
     <t>: im 1. Bericht (Planung) eintragen</t>
   </si>
@@ -124,27 +114,6 @@
     <t>Projektanfang</t>
   </si>
   <si>
-    <t>Ziellinie</t>
-  </si>
-  <si>
-    <t>Meilenstein 1</t>
-  </si>
-  <si>
-    <t>Meilenstein 2</t>
-  </si>
-  <si>
-    <t>Meilenstein 3</t>
-  </si>
-  <si>
-    <t>Meilenstein 4</t>
-  </si>
-  <si>
-    <t>Meilenstein 5</t>
-  </si>
-  <si>
-    <t>Meilenstein 6</t>
-  </si>
-  <si>
     <t>Woche</t>
   </si>
   <si>
@@ -152,9 +121,6 @@
   </si>
   <si>
     <t>Projekt:</t>
-  </si>
-  <si>
-    <t>Projektname</t>
   </si>
   <si>
     <t>Legende</t>
@@ -206,10 +172,6 @@
     <t>Sonstiges:</t>
   </si>
   <si>
-    <t>Hier kommen die Ergebnisse aus dem Berichtszeitraum.
-Meilensteinen sollen hier explizit erwähnt werden, sowie wichtige Projektschritte.</t>
-  </si>
-  <si>
     <t>Risiken:</t>
   </si>
   <si>
@@ -223,9 +185,6 @@
   </si>
   <si>
     <t>erreichte Meilensteine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meilenstein 7           </t>
   </si>
   <si>
     <t>Folgenummer:</t>
@@ -334,6 +293,36 @@
   </si>
   <si>
     <t>alexander.borrmann@stud.hs-emden-leer.de</t>
+  </si>
+  <si>
+    <t>Anforderungsanalyse und Aufwandseinschätzung</t>
+  </si>
+  <si>
+    <t>MoinMetrics</t>
+  </si>
+  <si>
+    <t>Anforderungsanalyse</t>
+  </si>
+  <si>
+    <t>Abschluss Systementwurf</t>
+  </si>
+  <si>
+    <t>Abschluss Implementierung</t>
+  </si>
+  <si>
+    <t>Integrations-/Systemtests</t>
+  </si>
+  <si>
+    <t>Abnahmetest</t>
+  </si>
+  <si>
+    <t>Systemarchitektur freigeben</t>
+  </si>
+  <si>
+    <t>Abschluss Software-Architektur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anforderungen wurden definiert. </t>
   </si>
 </sst>
 </file>
@@ -958,9 +947,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1041,9 +1027,6 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1168,6 +1151,33 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1251,29 +1261,8 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1457,37 +1446,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -1520,37 +1509,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -1619,37 +1608,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -1682,28 +1671,28 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4776119402985072E-2</c:v>
+                  <c:v>2.3255813953488372E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13432835820895522</c:v>
+                  <c:v>6.9767441860465115E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21791044776119403</c:v>
+                  <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35820895522388058</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37014925373134328</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45970149253731341</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57910447761194028</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -2087,37 +2076,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -2150,37 +2139,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -2249,28 +2238,28 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4776119402985072E-2</c:v>
+                  <c:v>2.3255813953488372E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13432835820895522</c:v>
+                  <c:v>6.9767441860465115E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21791044776119403</c:v>
+                  <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35820895522388058</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37014925373134328</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45970149253731341</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57910447761194028</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -2312,28 +2301,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14000000000000001</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.42</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.48</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.6</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2664,9 +2638,6 @@
               <c:f>MTA!$B$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Ziellinie</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2688,58 +2659,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2751,58 +2722,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2823,7 +2794,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 1</c:v>
+                  <c:v>Anforderungsanalyse</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2858,67 +2829,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2930,13 +2892,19 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38727</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38727</c:v>
+                  <c:v>46327</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46327</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46317</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38729</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2957,7 +2925,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 2</c:v>
+                  <c:v>Systemarchitektur freigeben</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2992,67 +2960,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3064,16 +3023,19 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38735</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38735</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38737</c:v>
+                  <c:v>46334</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>38737</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3094,7 +3056,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 3</c:v>
+                  <c:v>Abschluss Systementwurf</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3129,67 +3091,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3201,28 +3154,19 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38760</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38760</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38760</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38760</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38762</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38762</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38764</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3243,7 +3187,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 4</c:v>
+                  <c:v>Abschluss Software-Architektur</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3278,67 +3222,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3350,31 +3285,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38783</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38783</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38784</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38786</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38786</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38784</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38784</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38784</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38786</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -3398,7 +3318,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 5</c:v>
+                  <c:v>Abschluss Implementierung</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3433,67 +3353,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3505,31 +3416,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38790</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38790</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38790</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38792</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38795</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -3553,7 +3449,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 6</c:v>
+                  <c:v>Integrations-/Systemtests</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3588,67 +3484,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3660,31 +3547,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38797</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38797</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38797</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38798</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38800</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -3708,7 +3580,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 7           </c:v>
+                  <c:v>Abnahmetest</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3743,67 +3615,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3815,31 +3678,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>38803</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38803</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38803</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38803</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38803</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38806</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38806</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38806</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38806</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -3869,8 +3717,8 @@
         <c:axId val="504144584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="38837"/>
-          <c:min val="38718"/>
+          <c:max val="46411"/>
+          <c:min val="46292"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3916,8 +3764,8 @@
         <c:axId val="504151000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="38837"/>
-          <c:min val="38718"/>
+          <c:max val="46411"/>
+          <c:min val="46292"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4123,9 +3971,6 @@
               <c:f>MTA!$B$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Ziellinie</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -4147,58 +3992,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4210,58 +4055,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4282,7 +4127,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 1</c:v>
+                  <c:v>Anforderungsanalyse</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4317,67 +4162,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4389,13 +4225,19 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38727</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38727</c:v>
+                  <c:v>46327</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46327</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46317</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38729</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4416,7 +4258,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 2</c:v>
+                  <c:v>Systemarchitektur freigeben</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4451,67 +4293,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4523,16 +4356,19 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38735</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38735</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38737</c:v>
+                  <c:v>46334</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>38737</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4553,7 +4389,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 3</c:v>
+                  <c:v>Abschluss Systementwurf</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4588,67 +4424,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4660,28 +4487,19 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38760</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38760</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38760</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38760</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38762</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38762</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38764</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4702,7 +4520,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 4</c:v>
+                  <c:v>Abschluss Software-Architektur</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4737,67 +4555,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4809,31 +4618,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38783</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38783</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38784</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38786</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38786</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38784</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38784</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38784</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38786</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -4857,7 +4651,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 5</c:v>
+                  <c:v>Abschluss Implementierung</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4892,67 +4686,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4964,31 +4749,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38790</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38790</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38790</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38792</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38794</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38795</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -5012,7 +4782,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 6</c:v>
+                  <c:v>Integrations-/Systemtests</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5047,67 +4817,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5119,31 +4880,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>38797</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38797</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38797</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38798</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38800</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38800</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -5167,7 +4913,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Meilenstein 7           </c:v>
+                  <c:v>Abnahmetest</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5202,67 +4948,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38725</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38732</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38739</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38746</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38753</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38760</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38767</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38774</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38781</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38788</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38795</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38802</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38809</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38816</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38823</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38830</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38837</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>38729</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>38737</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>38766</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5274,31 +5011,16 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>38803</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38803</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38803</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38803</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38803</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38806</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38806</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>38806</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>38806</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>0</c:v>
@@ -5328,8 +5050,8 @@
         <c:axId val="504248024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="38837"/>
-          <c:min val="38718"/>
+          <c:max val="46411"/>
+          <c:min val="46292"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -5421,8 +5143,8 @@
         <c:axId val="504257128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="38837"/>
-          <c:min val="38718"/>
+          <c:max val="46411"/>
+          <c:min val="46292"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5700,37 +5422,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -5763,37 +5485,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -5862,37 +5584,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -5925,28 +5647,28 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4776119402985072E-2</c:v>
+                  <c:v>2.3255813953488372E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13432835820895522</c:v>
+                  <c:v>6.9767441860465115E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21791044776119403</c:v>
+                  <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35820895522388058</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37014925373134328</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45970149253731341</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57910447761194028</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6350,13 +6072,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.3</c:v>
@@ -6371,16 +6093,16 @@
                   <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.65</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.7</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -6398,28 +6120,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14000000000000001</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.42</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.48</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.6</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6458,13 +6165,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.3</c:v>
@@ -6479,16 +6186,16 @@
                   <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.65</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.7</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -6506,13 +6213,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.3</c:v>
@@ -6527,16 +6234,16 @@
                   <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.65</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.7</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -6864,58 +6571,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46293</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38724</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38731</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38738</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38745</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38752</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38759</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38766</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38773</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38780</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38787</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38794</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38801</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38808</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38815</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38822</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38829</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38836</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6927,43 +6634,43 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>20.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="11">
                   <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="12">
                   <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7007,58 +6714,58 @@
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>38718</c:v>
+                  <c:v>46293</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38724</c:v>
+                  <c:v>46299</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38731</c:v>
+                  <c:v>46306</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38738</c:v>
+                  <c:v>46313</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38745</c:v>
+                  <c:v>46320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38752</c:v>
+                  <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38759</c:v>
+                  <c:v>46334</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38766</c:v>
+                  <c:v>46341</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38773</c:v>
+                  <c:v>46348</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38780</c:v>
+                  <c:v>46355</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38787</c:v>
+                  <c:v>46362</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>38794</c:v>
+                  <c:v>46369</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>38801</c:v>
+                  <c:v>46376</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>38808</c:v>
+                  <c:v>46383</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38815</c:v>
+                  <c:v>46390</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>38822</c:v>
+                  <c:v>46397</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>38829</c:v>
+                  <c:v>46404</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>38836</c:v>
+                  <c:v>46411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7073,28 +6780,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>40</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7155,55 +6847,55 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>125</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>155</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>185</c:v>
+                  <c:v>104</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>215</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>245</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>275</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>305</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>335</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>335</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>335</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>335</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>335</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>335</c:v>
+                  <c:v>215</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7250,55 +6942,55 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>45</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>73</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>100</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>120</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>124</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>154</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>194</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7658,37 +7350,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -7721,37 +7413,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -7820,37 +7512,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -7883,13 +7575,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.3</c:v>
@@ -7904,16 +7596,16 @@
                   <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.65</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.7</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -8273,37 +7965,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -8336,37 +8028,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4626865671641784E-2</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14925373134328357</c:v>
+                  <c:v>9.3023255813953487E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22388059701492538</c:v>
+                  <c:v>0.16279069767441862</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0.23255813953488372</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37313432835820898</c:v>
+                  <c:v>0.31627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.46268656716417911</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.55223880597014929</c:v>
+                  <c:v>0.48372093023255813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.64179104477611937</c:v>
+                  <c:v>0.56744186046511624</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73134328358208955</c:v>
+                  <c:v>0.65116279069767447</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.82089552238805974</c:v>
+                  <c:v>0.76744186046511631</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.91044776119402981</c:v>
+                  <c:v>0.88372093023255816</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -8435,28 +8127,28 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4776119402985072E-2</c:v>
+                  <c:v>2.3255813953488372E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13432835820895522</c:v>
+                  <c:v>6.9767441860465115E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21791044776119403</c:v>
+                  <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.29850746268656714</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35820895522388058</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.37014925373134328</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.45970149253731341</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.57910447761194028</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -8498,28 +8190,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14000000000000001</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.31</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.42</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.48</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.52</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.6</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9476,74 +9153,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J1" s="124" t="s">
-        <v>79</v>
+      <c r="J1" s="122" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="139" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="J2" s="125"/>
+        <v>22</v>
+      </c>
+      <c r="B2" s="146" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="J2" s="123"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="93">
-        <v>42289</v>
-      </c>
-      <c r="C3" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="95">
+        <v>26</v>
+      </c>
+      <c r="B3" s="91">
+        <v>46307</v>
+      </c>
+      <c r="C3" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="93">
         <f>B3+B4-1</f>
-        <v>42295</v>
-      </c>
-      <c r="E3" s="96" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="84">
-        <v>8</v>
-      </c>
-      <c r="G3" s="96" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="97">
-        <v>38768</v>
-      </c>
-      <c r="J3" s="125" t="s">
-        <v>76</v>
+        <v>46313</v>
+      </c>
+      <c r="E3" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="82">
+        <v>4</v>
+      </c>
+      <c r="G3" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="95">
+        <f ca="1">TODAY()</f>
+        <v>46317</v>
+      </c>
+      <c r="J3" s="123" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="98">
+        <v>41</v>
+      </c>
+      <c r="B4" s="96">
         <v>7</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="123" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" s="125" t="s">
-        <v>77</v>
+      <c r="C4" s="97"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="121" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="123" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9552,90 +9230,96 @@
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
       <c r="E5" s="14" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="125"/>
+        <v>2</v>
+      </c>
+      <c r="J5" s="123"/>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="141" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="142"/>
-      <c r="D6" s="142"/>
-      <c r="E6" s="120" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="85"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="87">
-        <v>123456</v>
-      </c>
-      <c r="J6" s="125"/>
+        <v>25</v>
+      </c>
+      <c r="B6" s="148" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="118" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="83"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="85">
+        <v>7026074</v>
+      </c>
+      <c r="J6" s="123"/>
     </row>
     <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="135" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="120" t="s">
-        <v>91</v>
+        <v>25</v>
+      </c>
+      <c r="B7" s="142" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="143"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="118" t="s">
+        <v>78</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="88"/>
-      <c r="J7" s="125"/>
+      <c r="H7" s="86">
+        <v>7026439</v>
+      </c>
+      <c r="J7" s="123"/>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="135" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="120" t="s">
-        <v>92</v>
+        <v>25</v>
+      </c>
+      <c r="B8" s="142" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="143"/>
+      <c r="D8" s="143"/>
+      <c r="E8" s="118" t="s">
+        <v>79</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="88"/>
-      <c r="J8" s="125"/>
+      <c r="H8" s="86">
+        <v>7026303</v>
+      </c>
+      <c r="J8" s="123"/>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="137" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="89" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="92"/>
-      <c r="J9" s="125"/>
+        <v>25</v>
+      </c>
+      <c r="B9" s="144" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="145"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="87" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="89" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="123"/>
     </row>
     <row r="10" spans="1:10" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
@@ -9646,42 +9330,42 @@
       <c r="F10" s="11"/>
       <c r="G10" s="13"/>
       <c r="H10" s="4"/>
-      <c r="J10" s="125"/>
+      <c r="J10" s="123"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="143" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="85" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="86"/>
-      <c r="H11" s="102"/>
-      <c r="J11" s="125"/>
+        <v>28</v>
+      </c>
+      <c r="B11" s="150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="118" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="84"/>
+      <c r="H11" s="100"/>
+      <c r="J11" s="123"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="145" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="83"/>
-      <c r="J12" s="125" t="s">
-        <v>78</v>
+        <v>29</v>
+      </c>
+      <c r="B12" s="152" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="81"/>
+      <c r="J12" s="123" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -9694,12 +9378,12 @@
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
-      <c r="J13" s="125"/>
+      <c r="J13" s="123"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29"/>
       <c r="B14" s="6" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -9708,133 +9392,133 @@
       <c r="G14" s="30"/>
       <c r="H14"/>
       <c r="I14"/>
-      <c r="J14" s="125"/>
+      <c r="J14" s="123"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="126" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="127"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="128"/>
+        <v>35</v>
+      </c>
+      <c r="B15" s="133" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="134"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="135"/>
       <c r="I15"/>
-      <c r="J15" s="125" t="s">
-        <v>80</v>
+      <c r="J15" s="123" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="129"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="131"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
+      <c r="H16" s="138"/>
       <c r="I16"/>
-      <c r="J16" s="125"/>
+      <c r="J16" s="123"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="129"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="131"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="138"/>
       <c r="I17"/>
-      <c r="J17" s="125"/>
+      <c r="J17" s="123"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="129"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="131"/>
+      <c r="B18" s="136"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+      <c r="H18" s="138"/>
       <c r="I18"/>
-      <c r="J18" s="125"/>
+      <c r="J18" s="123"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="129"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="131"/>
+      <c r="B19" s="136"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="138"/>
       <c r="I19"/>
-      <c r="J19" s="125"/>
+      <c r="J19" s="123"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="129"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="130"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="131"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="138"/>
       <c r="I20"/>
-      <c r="J20" s="125"/>
+      <c r="J20" s="123"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="129"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="130"/>
-      <c r="E21" s="130"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="131"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="138"/>
       <c r="I21"/>
-      <c r="J21" s="125"/>
+      <c r="J21" s="123"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="129"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="130"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="131"/>
+      <c r="B22" s="136"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="138"/>
       <c r="I22"/>
-      <c r="J22" s="125"/>
+      <c r="J22" s="123"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="129"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="130"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="131"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="138"/>
       <c r="I23"/>
-      <c r="J23" s="125"/>
+      <c r="J23" s="123"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="132"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="134"/>
+      <c r="B24" s="139"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="141"/>
       <c r="I24"/>
-      <c r="J24" s="125"/>
+      <c r="J24" s="123"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
@@ -9846,83 +9530,83 @@
       <c r="G25" s="31"/>
       <c r="H25" s="32"/>
       <c r="I25"/>
-      <c r="J25" s="125"/>
+      <c r="J25" s="123"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="126" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="127"/>
-      <c r="D26" s="127"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="127"/>
-      <c r="G26" s="127"/>
-      <c r="H26" s="128"/>
+        <v>39</v>
+      </c>
+      <c r="B26" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="134"/>
+      <c r="D26" s="134"/>
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="135"/>
       <c r="I26"/>
-      <c r="J26" s="125"/>
+      <c r="J26" s="123"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="129"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="130"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="131"/>
+      <c r="B27" s="136"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="138"/>
       <c r="I27"/>
-      <c r="J27" s="125"/>
+      <c r="J27" s="123"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
-      <c r="B28" s="129"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="131"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="138"/>
       <c r="I28"/>
-      <c r="J28" s="125"/>
+      <c r="J28" s="123"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="129"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
-      <c r="E29" s="130"/>
-      <c r="F29" s="130"/>
-      <c r="G29" s="130"/>
-      <c r="H29" s="131"/>
+      <c r="B29" s="136"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="138"/>
       <c r="I29"/>
-      <c r="J29" s="125"/>
+      <c r="J29" s="123"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="129"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="130"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="131"/>
+      <c r="B30" s="136"/>
+      <c r="C30" s="137"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="138"/>
       <c r="I30"/>
-      <c r="J30" s="125"/>
+      <c r="J30" s="123"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="132"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="134"/>
+      <c r="B31" s="139"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="140"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="140"/>
+      <c r="H31" s="141"/>
       <c r="I31"/>
-      <c r="J31" s="125"/>
+      <c r="J31" s="123"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
@@ -9934,59 +9618,59 @@
       <c r="G32" s="32"/>
       <c r="H32" s="32"/>
       <c r="I32"/>
-      <c r="J32" s="125"/>
+      <c r="J32" s="123"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="126" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="127"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="128"/>
+        <v>37</v>
+      </c>
+      <c r="B33" s="133" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="134"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="134"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="135"/>
       <c r="I33"/>
-      <c r="J33" s="125"/>
+      <c r="J33" s="123"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="129"/>
-      <c r="C34" s="130"/>
-      <c r="D34" s="130"/>
-      <c r="E34" s="130"/>
-      <c r="F34" s="130"/>
-      <c r="G34" s="130"/>
-      <c r="H34" s="131"/>
+      <c r="B34" s="136"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="137"/>
+      <c r="G34" s="137"/>
+      <c r="H34" s="138"/>
       <c r="I34"/>
-      <c r="J34" s="125"/>
+      <c r="J34" s="123"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
-      <c r="B35" s="129"/>
-      <c r="C35" s="130"/>
-      <c r="D35" s="130"/>
-      <c r="E35" s="130"/>
-      <c r="F35" s="130"/>
-      <c r="G35" s="130"/>
-      <c r="H35" s="131"/>
+      <c r="B35" s="136"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="138"/>
       <c r="I35"/>
-      <c r="J35" s="125"/>
+      <c r="J35" s="123"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
-      <c r="B36" s="132"/>
-      <c r="C36" s="133"/>
-      <c r="D36" s="133"/>
-      <c r="E36" s="133"/>
-      <c r="F36" s="133"/>
-      <c r="G36" s="133"/>
-      <c r="H36" s="134"/>
+      <c r="B36" s="139"/>
+      <c r="C36" s="140"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="140"/>
+      <c r="G36" s="140"/>
+      <c r="H36" s="141"/>
       <c r="I36"/>
-      <c r="J36" s="125"/>
+      <c r="J36" s="123"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
@@ -9998,83 +9682,83 @@
       <c r="G37" s="32"/>
       <c r="H37" s="32"/>
       <c r="I37"/>
-      <c r="J37" s="125"/>
+      <c r="J37" s="123"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="126" t="s">
-        <v>1</v>
-      </c>
-      <c r="C38" s="127"/>
-      <c r="D38" s="127"/>
-      <c r="E38" s="127"/>
-      <c r="F38" s="127"/>
-      <c r="G38" s="127"/>
-      <c r="H38" s="128"/>
+        <v>38</v>
+      </c>
+      <c r="B38" s="133" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="134"/>
+      <c r="D38" s="134"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="134"/>
+      <c r="H38" s="135"/>
       <c r="I38"/>
-      <c r="J38" s="125"/>
+      <c r="J38" s="123"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="33"/>
-      <c r="B39" s="129"/>
-      <c r="C39" s="130"/>
-      <c r="D39" s="130"/>
-      <c r="E39" s="130"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="130"/>
-      <c r="H39" s="131"/>
+      <c r="B39" s="136"/>
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="137"/>
+      <c r="H39" s="138"/>
       <c r="I39"/>
-      <c r="J39" s="125"/>
+      <c r="J39" s="123"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="33"/>
-      <c r="B40" s="129"/>
-      <c r="C40" s="130"/>
-      <c r="D40" s="130"/>
-      <c r="E40" s="130"/>
-      <c r="F40" s="130"/>
-      <c r="G40" s="130"/>
-      <c r="H40" s="131"/>
+      <c r="B40" s="136"/>
+      <c r="C40" s="137"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="137"/>
+      <c r="G40" s="137"/>
+      <c r="H40" s="138"/>
       <c r="I40"/>
-      <c r="J40" s="125"/>
+      <c r="J40" s="123"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="33"/>
-      <c r="B41" s="129"/>
-      <c r="C41" s="130"/>
-      <c r="D41" s="130"/>
-      <c r="E41" s="130"/>
-      <c r="F41" s="130"/>
-      <c r="G41" s="130"/>
-      <c r="H41" s="131"/>
+      <c r="B41" s="136"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="137"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="137"/>
+      <c r="G41" s="137"/>
+      <c r="H41" s="138"/>
       <c r="I41"/>
-      <c r="J41" s="125"/>
+      <c r="J41" s="123"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="33"/>
-      <c r="B42" s="129"/>
-      <c r="C42" s="130"/>
-      <c r="D42" s="130"/>
-      <c r="E42" s="130"/>
-      <c r="F42" s="130"/>
-      <c r="G42" s="130"/>
-      <c r="H42" s="131"/>
+      <c r="B42" s="136"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="137"/>
+      <c r="G42" s="137"/>
+      <c r="H42" s="138"/>
       <c r="I42"/>
-      <c r="J42" s="125"/>
+      <c r="J42" s="123"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="33"/>
-      <c r="B43" s="132"/>
-      <c r="C43" s="133"/>
-      <c r="D43" s="133"/>
-      <c r="E43" s="133"/>
-      <c r="F43" s="133"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="134"/>
+      <c r="B43" s="139"/>
+      <c r="C43" s="140"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140"/>
+      <c r="H43" s="141"/>
       <c r="I43"/>
-      <c r="J43" s="125"/>
+      <c r="J43" s="123"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44"/>
@@ -10086,7 +9770,7 @@
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44"/>
-      <c r="J44" s="125"/>
+      <c r="J44" s="123"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45"/>
@@ -10098,8 +9782,8 @@
       <c r="G45"/>
       <c r="H45"/>
       <c r="I45"/>
-      <c r="J45" s="125" t="s">
-        <v>81</v>
+      <c r="J45" s="123" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -10112,8 +9796,8 @@
       <c r="G46"/>
       <c r="H46"/>
       <c r="I46"/>
-      <c r="J46" s="125" t="s">
-        <v>82</v>
+      <c r="J46" s="123" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -10126,7 +9810,7 @@
       <c r="G47"/>
       <c r="H47"/>
       <c r="I47"/>
-      <c r="J47" s="125"/>
+      <c r="J47" s="123"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48"/>
@@ -10138,8 +9822,8 @@
       <c r="G48"/>
       <c r="H48"/>
       <c r="I48"/>
-      <c r="J48" s="125" t="s">
-        <v>83</v>
+      <c r="J48" s="123" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -10152,7 +9836,7 @@
       <c r="G49"/>
       <c r="H49"/>
       <c r="I49"/>
-      <c r="J49" s="125"/>
+      <c r="J49" s="123"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50"/>
@@ -10164,7 +9848,7 @@
       <c r="G50"/>
       <c r="H50"/>
       <c r="I50"/>
-      <c r="J50" s="125"/>
+      <c r="J50" s="123"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51"/>
@@ -10176,7 +9860,7 @@
       <c r="G51"/>
       <c r="H51"/>
       <c r="I51"/>
-      <c r="J51" s="125"/>
+      <c r="J51" s="123"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52"/>
@@ -10188,7 +9872,7 @@
       <c r="G52"/>
       <c r="H52"/>
       <c r="I52"/>
-      <c r="J52" s="125"/>
+      <c r="J52" s="123"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53"/>
@@ -10200,7 +9884,7 @@
       <c r="G53"/>
       <c r="H53"/>
       <c r="I53"/>
-      <c r="J53" s="125"/>
+      <c r="J53" s="123"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54"/>
@@ -10212,7 +9896,7 @@
       <c r="G54"/>
       <c r="H54"/>
       <c r="I54"/>
-      <c r="J54" s="125"/>
+      <c r="J54" s="123"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55"/>
@@ -10224,7 +9908,7 @@
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55"/>
-      <c r="J55" s="125"/>
+      <c r="J55" s="123"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56"/>
@@ -10236,7 +9920,7 @@
       <c r="G56"/>
       <c r="H56"/>
       <c r="I56"/>
-      <c r="J56" s="125"/>
+      <c r="J56" s="123"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57"/>
@@ -10248,7 +9932,7 @@
       <c r="G57"/>
       <c r="H57"/>
       <c r="I57"/>
-      <c r="J57" s="125"/>
+      <c r="J57" s="123"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58"/>
@@ -10260,7 +9944,7 @@
       <c r="G58"/>
       <c r="H58"/>
       <c r="I58"/>
-      <c r="J58" s="125"/>
+      <c r="J58" s="123"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59"/>
@@ -10272,7 +9956,7 @@
       <c r="G59"/>
       <c r="H59"/>
       <c r="I59"/>
-      <c r="J59" s="125"/>
+      <c r="J59" s="123"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60"/>
@@ -10284,7 +9968,7 @@
       <c r="G60"/>
       <c r="H60"/>
       <c r="I60"/>
-      <c r="J60" s="125"/>
+      <c r="J60" s="123"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61"/>
@@ -10296,7 +9980,7 @@
       <c r="G61"/>
       <c r="H61"/>
       <c r="I61"/>
-      <c r="J61" s="125"/>
+      <c r="J61" s="123"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62"/>
@@ -10308,7 +9992,7 @@
       <c r="G62"/>
       <c r="H62"/>
       <c r="I62"/>
-      <c r="J62" s="125"/>
+      <c r="J62" s="123"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63"/>
@@ -10320,7 +10004,7 @@
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63"/>
-      <c r="J63" s="125"/>
+      <c r="J63" s="123"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64"/>
@@ -10332,7 +10016,7 @@
       <c r="G64"/>
       <c r="H64"/>
       <c r="I64"/>
-      <c r="J64" s="125"/>
+      <c r="J64" s="123"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65"/>
@@ -10344,7 +10028,7 @@
       <c r="G65"/>
       <c r="H65"/>
       <c r="I65"/>
-      <c r="J65" s="125"/>
+      <c r="J65" s="123"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66"/>
@@ -10359,15 +10043,15 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67"/>
-      <c r="B67" s="140" t="s">
-        <v>84</v>
-      </c>
-      <c r="C67" s="140"/>
-      <c r="D67" s="140"/>
-      <c r="E67" s="140"/>
-      <c r="F67" s="140"/>
-      <c r="G67" s="140"/>
-      <c r="H67" s="140"/>
+      <c r="B67" s="147" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="147"/>
+      <c r="D67" s="147"/>
+      <c r="E67" s="147"/>
+      <c r="F67" s="147"/>
+      <c r="G67" s="147"/>
+      <c r="H67" s="147"/>
       <c r="I67"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -10465,95 +10149,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="121" t="s">
-        <v>22</v>
+      <c r="A1" s="119" t="s">
+        <v>19</v>
       </c>
       <c r="B1" s="7">
-        <v>38718</v>
+        <v>46292</v>
       </c>
       <c r="C1" s="18"/>
       <c r="I1" s="19" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B2" s="23">
         <v>7</v>
       </c>
       <c r="C2" s="18"/>
       <c r="I2" s="20" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="K2" s="38"/>
     </row>
     <row r="3" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E3" s="10"/>
-      <c r="I3" s="112"/>
+      <c r="I3" s="110"/>
     </row>
     <row r="4" spans="1:13" s="5" customFormat="1" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="104" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="105" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="105" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="105" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="105" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="106" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="107" t="s">
-        <v>56</v>
+        <v>18</v>
+      </c>
+      <c r="B4" s="108"/>
+      <c r="C4" s="102" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="103" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="104" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="105" t="s">
+        <v>86</v>
       </c>
       <c r="J4" s="39"/>
-      <c r="K4" s="41"/>
+      <c r="K4" s="154"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <f>B1</f>
-        <v>38718</v>
-      </c>
-      <c r="B5" s="111">
+        <v>46292</v>
+      </c>
+      <c r="B5" s="109">
         <f>A5</f>
-        <v>38718</v>
-      </c>
-      <c r="C5" s="103">
-        <v>38727</v>
-      </c>
-      <c r="D5" s="103">
-        <v>38735</v>
-      </c>
-      <c r="E5" s="103">
-        <v>38760</v>
-      </c>
-      <c r="F5" s="103">
-        <v>38783</v>
-      </c>
-      <c r="G5" s="103">
-        <v>38790</v>
-      </c>
-      <c r="H5" s="103">
-        <v>38797</v>
-      </c>
-      <c r="I5" s="103">
-        <v>38803</v>
+        <v>46292</v>
+      </c>
+      <c r="C5" s="101">
+        <v>46327</v>
+      </c>
+      <c r="D5" s="101">
+        <v>46334</v>
+      </c>
+      <c r="E5" s="101">
+        <v>46341</v>
+      </c>
+      <c r="F5" s="101">
+        <v>46348</v>
+      </c>
+      <c r="G5" s="101">
+        <v>46355</v>
+      </c>
+      <c r="H5" s="101">
+        <v>46362</v>
+      </c>
+      <c r="I5" s="101">
+        <v>46369</v>
       </c>
       <c r="J5" s="40" t="str">
         <f>IF(B5&gt;$K$23,B5,"")</f>
@@ -10561,43 +10243,43 @@
       </c>
       <c r="K5" s="40">
         <f>MAX(C5:I5)</f>
-        <v>38803</v>
+        <v>46369</v>
       </c>
       <c r="L5" s="27"/>
       <c r="M5" s="36">
         <f>IF(L5=0,B5,"")</f>
-        <v>38718</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <f>A5+$B$2</f>
-        <v>38725</v>
-      </c>
-      <c r="B6" s="111">
+        <v>46299</v>
+      </c>
+      <c r="B6" s="109">
         <f t="shared" ref="B6:B11" si="0">A6</f>
-        <v>38725</v>
-      </c>
-      <c r="C6" s="42">
-        <v>38727</v>
-      </c>
-      <c r="D6" s="42">
-        <v>38735</v>
-      </c>
-      <c r="E6" s="42">
-        <v>38760</v>
-      </c>
-      <c r="F6" s="42">
-        <v>38783</v>
-      </c>
-      <c r="G6" s="42">
-        <v>38790</v>
-      </c>
-      <c r="H6" s="42">
-        <v>38797</v>
-      </c>
-      <c r="I6" s="42">
-        <v>38803</v>
+        <v>46299</v>
+      </c>
+      <c r="C6" s="41">
+        <v>46327</v>
+      </c>
+      <c r="D6" s="41">
+        <v>46334</v>
+      </c>
+      <c r="E6" s="41">
+        <v>46341</v>
+      </c>
+      <c r="F6" s="41">
+        <v>46348</v>
+      </c>
+      <c r="G6" s="41">
+        <v>46355</v>
+      </c>
+      <c r="H6" s="41">
+        <v>46362</v>
+      </c>
+      <c r="I6" s="41">
+        <v>46369</v>
       </c>
       <c r="J6" s="40" t="str">
         <f t="shared" ref="J6:J22" si="1">IF(B6&gt;$K$23,B6,"")</f>
@@ -10605,41 +10287,43 @@
       </c>
       <c r="K6" s="40">
         <f t="shared" ref="K6:K22" si="2">MAX(C6:I6)</f>
-        <v>38803</v>
+        <v>46369</v>
       </c>
       <c r="L6" s="27"/>
       <c r="M6" s="36">
         <f t="shared" ref="M6:M22" si="3">IF(L6=0,B6,"")</f>
-        <v>38725</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <f t="shared" ref="A7:A22" si="4">A6+$B$2</f>
-        <v>38732</v>
-      </c>
-      <c r="B7" s="111">
+        <v>46306</v>
+      </c>
+      <c r="B7" s="109">
         <f t="shared" si="0"/>
-        <v>38732</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42">
-        <v>38737</v>
-      </c>
-      <c r="E7" s="42">
-        <v>38760</v>
-      </c>
-      <c r="F7" s="42">
-        <v>38784</v>
-      </c>
-      <c r="G7" s="42">
-        <v>38790</v>
-      </c>
-      <c r="H7" s="42">
-        <v>38797</v>
-      </c>
-      <c r="I7" s="42">
-        <v>38803</v>
+        <v>46306</v>
+      </c>
+      <c r="C7" s="41">
+        <v>46327</v>
+      </c>
+      <c r="D7" s="41">
+        <v>46334</v>
+      </c>
+      <c r="E7" s="41">
+        <v>46341</v>
+      </c>
+      <c r="F7" s="41">
+        <v>46348</v>
+      </c>
+      <c r="G7" s="41">
+        <v>46355</v>
+      </c>
+      <c r="H7" s="41">
+        <v>46362</v>
+      </c>
+      <c r="I7" s="41">
+        <v>46369</v>
       </c>
       <c r="J7" s="40" t="str">
         <f t="shared" si="1"/>
@@ -10647,39 +10331,43 @@
       </c>
       <c r="K7" s="40">
         <f t="shared" si="2"/>
-        <v>38803</v>
+        <v>46369</v>
       </c>
       <c r="L7" s="27"/>
       <c r="M7" s="36">
         <f t="shared" si="3"/>
-        <v>38732</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <f t="shared" si="4"/>
-        <v>38739</v>
-      </c>
-      <c r="B8" s="111">
+        <v>46313</v>
+      </c>
+      <c r="B8" s="109">
         <f t="shared" si="0"/>
-        <v>38739</v>
-      </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="42">
-        <v>38760</v>
-      </c>
-      <c r="F8" s="42">
-        <v>38786</v>
-      </c>
-      <c r="G8" s="42">
-        <v>38792</v>
-      </c>
-      <c r="H8" s="42">
-        <v>38798</v>
-      </c>
-      <c r="I8" s="42">
-        <v>38803</v>
+        <v>46313</v>
+      </c>
+      <c r="C8" s="41">
+        <v>46317</v>
+      </c>
+      <c r="D8" s="41">
+        <v>46334</v>
+      </c>
+      <c r="E8" s="41">
+        <v>46341</v>
+      </c>
+      <c r="F8" s="41">
+        <v>46348</v>
+      </c>
+      <c r="G8" s="41">
+        <v>46355</v>
+      </c>
+      <c r="H8" s="41">
+        <v>46362</v>
+      </c>
+      <c r="I8" s="41">
+        <v>46369</v>
       </c>
       <c r="J8" s="40" t="str">
         <f t="shared" si="1"/>
@@ -10687,226 +10375,180 @@
       </c>
       <c r="K8" s="40">
         <f t="shared" si="2"/>
-        <v>38803</v>
+        <v>46369</v>
       </c>
       <c r="L8" s="27"/>
       <c r="M8" s="36">
         <f t="shared" si="3"/>
-        <v>38739</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <f t="shared" si="4"/>
-        <v>38746</v>
-      </c>
-      <c r="B9" s="111">
+        <v>46320</v>
+      </c>
+      <c r="B9" s="109">
         <f t="shared" si="0"/>
-        <v>38746</v>
-      </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42">
-        <v>38762</v>
-      </c>
-      <c r="F9" s="42">
-        <v>38786</v>
-      </c>
-      <c r="G9" s="42">
-        <v>38794</v>
-      </c>
-      <c r="H9" s="42">
-        <v>38800</v>
-      </c>
-      <c r="I9" s="42">
-        <v>38803</v>
-      </c>
+        <v>46320</v>
+      </c>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
       <c r="J9" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K9" s="40">
         <f t="shared" si="2"/>
-        <v>38803</v>
+        <v>0</v>
       </c>
       <c r="L9" s="27"/>
       <c r="M9" s="36">
         <f t="shared" si="3"/>
-        <v>38746</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <f t="shared" si="4"/>
-        <v>38753</v>
-      </c>
-      <c r="B10" s="111">
+        <v>46327</v>
+      </c>
+      <c r="B10" s="109">
         <f t="shared" si="0"/>
-        <v>38753</v>
-      </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42">
-        <v>38762</v>
-      </c>
-      <c r="F10" s="42">
-        <v>38784</v>
-      </c>
-      <c r="G10" s="42">
-        <v>38794</v>
-      </c>
-      <c r="H10" s="42">
-        <v>38800</v>
-      </c>
-      <c r="I10" s="42">
-        <v>38806</v>
-      </c>
+        <v>46327</v>
+      </c>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
       <c r="J10" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K10" s="40">
         <f t="shared" si="2"/>
-        <v>38806</v>
+        <v>0</v>
       </c>
       <c r="L10" s="27"/>
       <c r="M10" s="36">
         <f t="shared" si="3"/>
-        <v>38753</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <f t="shared" si="4"/>
-        <v>38760</v>
-      </c>
-      <c r="B11" s="111">
+        <v>46334</v>
+      </c>
+      <c r="B11" s="109">
         <f t="shared" si="0"/>
-        <v>38760</v>
-      </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42">
-        <v>38764</v>
-      </c>
-      <c r="F11" s="42">
-        <v>38784</v>
-      </c>
-      <c r="G11" s="42">
-        <v>38794</v>
-      </c>
-      <c r="H11" s="42">
-        <v>38800</v>
-      </c>
-      <c r="I11" s="42">
-        <v>38806</v>
-      </c>
+        <v>46334</v>
+      </c>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
       <c r="J11" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K11" s="40">
         <f t="shared" si="2"/>
-        <v>38806</v>
+        <v>0</v>
       </c>
       <c r="L11" s="27"/>
       <c r="M11" s="36">
         <f t="shared" si="3"/>
-        <v>38760</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <f t="shared" si="4"/>
-        <v>38767</v>
-      </c>
-      <c r="B12" s="111">
+        <v>46341</v>
+      </c>
+      <c r="B12" s="109">
         <f t="shared" ref="B12:B22" si="5">A12</f>
-        <v>38767</v>
-      </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="42">
-        <v>38784</v>
-      </c>
-      <c r="G12" s="42">
-        <v>38794</v>
-      </c>
-      <c r="H12" s="42">
-        <v>38800</v>
-      </c>
-      <c r="I12" s="42">
-        <v>38806</v>
-      </c>
+        <v>46341</v>
+      </c>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
       <c r="J12" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K12" s="40">
         <f t="shared" si="2"/>
-        <v>38806</v>
+        <v>0</v>
       </c>
       <c r="L12" s="27"/>
       <c r="M12" s="36">
         <f t="shared" si="3"/>
-        <v>38767</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <f t="shared" si="4"/>
-        <v>38774</v>
-      </c>
-      <c r="B13" s="111">
+        <v>46348</v>
+      </c>
+      <c r="B13" s="109">
         <f t="shared" si="5"/>
-        <v>38774</v>
-      </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42">
-        <v>38786</v>
-      </c>
-      <c r="G13" s="42">
-        <v>38795</v>
-      </c>
-      <c r="H13" s="42">
-        <v>38800</v>
-      </c>
-      <c r="I13" s="42">
-        <v>38806</v>
-      </c>
+        <v>46348</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
       <c r="J13" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K13" s="40">
         <f t="shared" si="2"/>
-        <v>38806</v>
+        <v>0</v>
       </c>
       <c r="L13" s="27"/>
       <c r="M13" s="36">
         <f t="shared" si="3"/>
-        <v>38774</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <f t="shared" si="4"/>
-        <v>38781</v>
-      </c>
-      <c r="B14" s="111">
+        <v>46355</v>
+      </c>
+      <c r="B14" s="109">
         <f t="shared" si="5"/>
-        <v>38781</v>
-      </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
+        <v>46355</v>
+      </c>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
       <c r="J14" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10918,25 +10560,25 @@
       <c r="L14" s="27"/>
       <c r="M14" s="36">
         <f t="shared" si="3"/>
-        <v>38781</v>
+        <v>46355</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <f t="shared" si="4"/>
-        <v>38788</v>
-      </c>
-      <c r="B15" s="111">
+        <v>46362</v>
+      </c>
+      <c r="B15" s="109">
         <f t="shared" si="5"/>
-        <v>38788</v>
-      </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
+        <v>46362</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
       <c r="J15" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10948,25 +10590,25 @@
       <c r="L15" s="27"/>
       <c r="M15" s="36">
         <f t="shared" si="3"/>
-        <v>38788</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <f t="shared" si="4"/>
-        <v>38795</v>
-      </c>
-      <c r="B16" s="111">
+        <v>46369</v>
+      </c>
+      <c r="B16" s="109">
         <f t="shared" si="5"/>
-        <v>38795</v>
-      </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
+        <v>46369</v>
+      </c>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
       <c r="J16" s="40" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -10978,28 +10620,28 @@
       <c r="L16" s="27"/>
       <c r="M16" s="36">
         <f t="shared" si="3"/>
-        <v>38795</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <f t="shared" si="4"/>
-        <v>38802</v>
-      </c>
-      <c r="B17" s="111">
+        <v>46376</v>
+      </c>
+      <c r="B17" s="109">
         <f t="shared" si="5"/>
-        <v>38802</v>
-      </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="40" t="str">
+        <v>46376</v>
+      </c>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="40">
         <f t="shared" si="1"/>
-        <v/>
+        <v>46376</v>
       </c>
       <c r="K17" s="40">
         <f t="shared" si="2"/>
@@ -11008,28 +10650,28 @@
       <c r="L17" s="27"/>
       <c r="M17" s="36">
         <f t="shared" si="3"/>
-        <v>38802</v>
+        <v>46376</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <f t="shared" si="4"/>
-        <v>38809</v>
-      </c>
-      <c r="B18" s="111">
+        <v>46383</v>
+      </c>
+      <c r="B18" s="109">
         <f t="shared" si="5"/>
-        <v>38809</v>
-      </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="42"/>
+        <v>46383</v>
+      </c>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="41"/>
       <c r="J18" s="40">
         <f t="shared" si="1"/>
-        <v>38809</v>
+        <v>46383</v>
       </c>
       <c r="K18" s="40">
         <f t="shared" si="2"/>
@@ -11038,28 +10680,28 @@
       <c r="L18" s="27"/>
       <c r="M18" s="36">
         <f t="shared" si="3"/>
-        <v>38809</v>
+        <v>46383</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <f t="shared" si="4"/>
-        <v>38816</v>
-      </c>
-      <c r="B19" s="111">
+        <v>46390</v>
+      </c>
+      <c r="B19" s="109">
         <f t="shared" si="5"/>
-        <v>38816</v>
-      </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="42"/>
+        <v>46390</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="41"/>
       <c r="J19" s="40">
         <f t="shared" si="1"/>
-        <v>38816</v>
+        <v>46390</v>
       </c>
       <c r="K19" s="40">
         <f t="shared" si="2"/>
@@ -11068,28 +10710,28 @@
       <c r="L19" s="27"/>
       <c r="M19" s="36">
         <f t="shared" si="3"/>
-        <v>38816</v>
+        <v>46390</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <f t="shared" si="4"/>
-        <v>38823</v>
-      </c>
-      <c r="B20" s="111">
+        <v>46397</v>
+      </c>
+      <c r="B20" s="109">
         <f t="shared" si="5"/>
-        <v>38823</v>
-      </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="42"/>
+        <v>46397</v>
+      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="41"/>
       <c r="J20" s="40">
         <f t="shared" si="1"/>
-        <v>38823</v>
+        <v>46397</v>
       </c>
       <c r="K20" s="40">
         <f t="shared" si="2"/>
@@ -11098,28 +10740,28 @@
       <c r="L20" s="27"/>
       <c r="M20" s="36">
         <f t="shared" si="3"/>
-        <v>38823</v>
+        <v>46397</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <f t="shared" si="4"/>
-        <v>38830</v>
-      </c>
-      <c r="B21" s="111">
+        <v>46404</v>
+      </c>
+      <c r="B21" s="109">
         <f t="shared" si="5"/>
-        <v>38830</v>
-      </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
+        <v>46404</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
       <c r="J21" s="40">
         <f t="shared" si="1"/>
-        <v>38830</v>
+        <v>46404</v>
       </c>
       <c r="K21" s="40">
         <f t="shared" si="2"/>
@@ -11128,28 +10770,28 @@
       <c r="L21" s="27"/>
       <c r="M21" s="36">
         <f t="shared" si="3"/>
-        <v>38830</v>
+        <v>46404</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <f t="shared" si="4"/>
-        <v>38837</v>
-      </c>
-      <c r="B22" s="111">
+        <v>46411</v>
+      </c>
+      <c r="B22" s="109">
         <f t="shared" si="5"/>
-        <v>38837</v>
-      </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
+        <v>46411</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
       <c r="J22" s="40">
         <f t="shared" si="1"/>
-        <v>38837</v>
+        <v>46411</v>
       </c>
       <c r="K22" s="40">
         <f t="shared" si="2"/>
@@ -11158,7 +10800,7 @@
       <c r="L22" s="27"/>
       <c r="M22" s="36">
         <f t="shared" si="3"/>
-        <v>38837</v>
+        <v>46411</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -11172,17 +10814,17 @@
       <c r="I23" s="14"/>
       <c r="J23" s="40">
         <f>MIN(J5:J22)</f>
-        <v>38809</v>
+        <v>46376</v>
       </c>
       <c r="K23" s="40">
         <f>MAX(K5:K22)</f>
-        <v>38806</v>
+        <v>46369</v>
       </c>
       <c r="L23" s="28"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B24" s="25" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
@@ -11191,16 +10833,10 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="43">
-        <v>38729</v>
-      </c>
-      <c r="B25" t="str">
-        <f>C4</f>
-        <v>Meilenstein 1</v>
-      </c>
+      <c r="A25" s="42"/>
       <c r="C25" s="40">
         <f>A25</f>
-        <v>38729</v>
+        <v>0</v>
       </c>
       <c r="D25" s="40"/>
       <c r="E25" s="40"/>
@@ -11210,17 +10846,11 @@
       <c r="I25" s="36"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="43">
-        <v>38737</v>
-      </c>
-      <c r="B26" t="str">
-        <f>D4</f>
-        <v>Meilenstein 2</v>
-      </c>
+      <c r="A26" s="42"/>
       <c r="C26" s="36"/>
       <c r="D26" s="40">
         <f>A26</f>
-        <v>38737</v>
+        <v>0</v>
       </c>
       <c r="E26" s="36"/>
       <c r="F26" s="36"/>
@@ -11229,18 +10859,12 @@
       <c r="I26" s="36"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="43">
-        <v>38766</v>
-      </c>
-      <c r="B27" t="str">
-        <f>E4</f>
-        <v>Meilenstein 3</v>
-      </c>
+      <c r="A27" s="42"/>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
       <c r="E27" s="40">
         <f>A27</f>
-        <v>38766</v>
+        <v>0</v>
       </c>
       <c r="F27" s="36"/>
       <c r="G27" s="36"/>
@@ -11248,11 +10872,7 @@
       <c r="I27" s="36"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="43"/>
-      <c r="B28" t="str">
-        <f>F4</f>
-        <v>Meilenstein 4</v>
-      </c>
+      <c r="A28" s="42"/>
       <c r="C28" s="36"/>
       <c r="D28" s="36"/>
       <c r="E28" s="36"/>
@@ -11265,11 +10885,7 @@
       <c r="I28" s="36"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="43"/>
-      <c r="B29" t="str">
-        <f>G4</f>
-        <v>Meilenstein 5</v>
-      </c>
+      <c r="A29" s="42"/>
       <c r="C29" s="36"/>
       <c r="D29" s="36"/>
       <c r="E29" s="36"/>
@@ -11282,11 +10898,7 @@
       <c r="I29" s="36"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="43"/>
-      <c r="B30" t="str">
-        <f>H4</f>
-        <v>Meilenstein 6</v>
-      </c>
+      <c r="A30" s="42"/>
       <c r="C30" s="36"/>
       <c r="D30" s="36"/>
       <c r="E30" s="36"/>
@@ -11299,11 +10911,7 @@
       <c r="I30" s="36"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="43"/>
-      <c r="B31" t="str">
-        <f>I4</f>
-        <v xml:space="preserve">Meilenstein 7           </v>
-      </c>
+      <c r="A31" s="42"/>
       <c r="C31" s="36"/>
       <c r="D31" s="36"/>
       <c r="E31" s="36"/>
@@ -11317,121 +10925,121 @@
       <c r="K31" s="40"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="115" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="116"/>
+      <c r="A33" s="113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="114"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="117" t="s">
+      <c r="A34" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="116">
+        <f>B5</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="115" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="117">
+        <f>B22</f>
+        <v>46411</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="115" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="117">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="115" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="115" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="117">
+        <f>B34</f>
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="118">
-        <f>B5</f>
-        <v>38718</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="117" t="s">
+      <c r="B39" s="112"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="B35" s="119">
-        <f>B22</f>
-        <v>38837</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="117" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="119">
+      <c r="B40" s="112"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="111" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="117" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="117" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="119">
-        <f>B34</f>
-        <v>38718</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
-        <v>18</v>
-      </c>
-      <c r="B39" s="114"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="114"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="112"/>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="113" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" s="114"/>
+      <c r="A42" s="111" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="112"/>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="114"/>
+      <c r="A43" s="111" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="112"/>
     </row>
     <row r="45" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="109" t="s">
-        <v>34</v>
+      <c r="A45" s="107" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="45"/>
+      <c r="A47" s="44"/>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="122" t="s">
-        <v>75</v>
+      <c r="A48" s="120" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="46"/>
+      <c r="A50" s="45"/>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="81"/>
+      <c r="A53" s="80"/>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="108" t="s">
-        <v>9</v>
+      <c r="A57" s="106" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -11447,7 +11055,7 @@
   </customSheetViews>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.26" right="0.31" top="1" bottom="1" header="0.49" footer="0.4921259845"/>
-  <pageSetup paperSize="9" scale="49" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="54" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">
@@ -11482,19 +11090,19 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B1" s="17">
         <f>MTA!B1</f>
-        <v>38718</v>
+        <v>46292</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B2" s="14">
         <f>MTA!B2</f>
@@ -11502,7 +11110,7 @@
       </c>
       <c r="C2" s="17"/>
       <c r="K2" s="20" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -11511,758 +11119,737 @@
       <c r="K3" s="20"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="153" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="154"/>
-      <c r="D4" s="149" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="151" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="152"/>
+      <c r="A4" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="131" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="132"/>
+      <c r="D4" s="127" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="129" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="130"/>
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="125" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="126"/>
+      <c r="D5" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="69">
+        <v>46293</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="147" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="148"/>
-      <c r="D5" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="70">
-        <f>B1</f>
-        <v>38718</v>
-      </c>
-      <c r="B6" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="73">
+      <c r="C6" s="72">
         <f t="shared" ref="C6:C18" si="0">A6</f>
-        <v>38718</v>
-      </c>
-      <c r="D6" s="76">
+        <v>46293</v>
+      </c>
+      <c r="D6" s="75">
+        <v>20.5</v>
+      </c>
+      <c r="E6" s="58">
         <v>0</v>
       </c>
-      <c r="E6" s="59">
-        <v>0</v>
-      </c>
-      <c r="F6" s="60">
+      <c r="F6" s="59">
         <f>E6/MAX(E$6:E$23)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="59">
+      <c r="G6" s="58">
         <v>0</v>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="58">
         <v>0</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="60">
         <f>IF(ISBLANK(G6),"",H6/MAX(E$6:E$23))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="59">
         <v>0</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="60">
         <v>0</v>
       </c>
       <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="71">
+      <c r="A7" s="70">
         <f>A6-1+$B$2</f>
-        <v>38724</v>
-      </c>
-      <c r="B7" s="62">
+        <v>46299</v>
+      </c>
+      <c r="B7" s="61">
         <f>C6</f>
-        <v>38718</v>
-      </c>
-      <c r="C7" s="74">
+        <v>46293</v>
+      </c>
+      <c r="C7" s="73">
         <f t="shared" si="0"/>
-        <v>38724</v>
-      </c>
-      <c r="D7" s="77">
-        <v>25</v>
+        <v>46299</v>
+      </c>
+      <c r="D7" s="76">
+        <v>10</v>
       </c>
       <c r="E7" s="22">
         <f>IF(ISBLANK(D7),E6,E6+D7)</f>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F7" s="35">
         <f>E7/MAX(E$6:E$23)</f>
-        <v>7.4626865671641784E-2</v>
-      </c>
-      <c r="G7" s="49">
-        <v>15</v>
+        <v>4.6511627906976744E-2</v>
+      </c>
+      <c r="G7" s="48">
+        <v>5</v>
       </c>
       <c r="H7" s="22">
         <f>IF(G7="",H6,H6+G7)</f>
-        <v>15</v>
-      </c>
-      <c r="I7" s="78">
+        <v>5</v>
+      </c>
+      <c r="I7" s="77">
         <f>H7/MAX(E$6:E$23)</f>
-        <v>4.4776119402985072E-2</v>
-      </c>
-      <c r="J7" s="50">
-        <v>0.1</v>
-      </c>
-      <c r="K7" s="63">
-        <v>0.12</v>
+        <v>2.3255813953488372E-2</v>
+      </c>
+      <c r="J7" s="49">
+        <v>0.05</v>
+      </c>
+      <c r="K7" s="62">
+        <v>0.05</v>
       </c>
       <c r="M7" s="5"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="71">
+      <c r="A8" s="70">
         <f t="shared" ref="A8:A23" si="1">A7+$B$2</f>
-        <v>38731</v>
-      </c>
-      <c r="B8" s="62">
+        <v>46306</v>
+      </c>
+      <c r="B8" s="61">
         <f t="shared" ref="B8:B18" si="2">C7+1</f>
-        <v>38725</v>
-      </c>
-      <c r="C8" s="74">
+        <v>46300</v>
+      </c>
+      <c r="C8" s="73">
         <f t="shared" si="0"/>
-        <v>38731</v>
-      </c>
-      <c r="D8" s="77">
-        <v>25</v>
+        <v>46306</v>
+      </c>
+      <c r="D8" s="76">
+        <v>10</v>
       </c>
       <c r="E8" s="22">
         <f t="shared" ref="E8:E23" si="3">IF(ISBLANK(D8),E7,E7+D8)</f>
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F8" s="35">
         <f t="shared" ref="F8:F23" si="4">E8/MAX(E$6:E$23)</f>
-        <v>0.14925373134328357</v>
-      </c>
-      <c r="G8" s="49">
-        <v>30</v>
+        <v>9.3023255813953487E-2</v>
+      </c>
+      <c r="G8" s="48">
+        <v>10</v>
       </c>
       <c r="H8" s="22">
         <f t="shared" ref="H8:H23" si="5">IF(G8="",H7,H7+G8)</f>
-        <v>45</v>
-      </c>
-      <c r="I8" s="78">
+        <v>15</v>
+      </c>
+      <c r="I8" s="77">
         <f t="shared" ref="I8:I23" si="6">IF(ISBLANK(G8),0,H8/MAX(E$6:E$23))</f>
-        <v>0.13432835820895522</v>
-      </c>
-      <c r="J8" s="50">
-        <v>0.15</v>
-      </c>
-      <c r="K8" s="63">
-        <v>0.14000000000000001</v>
+        <v>6.9767441860465115E-2</v>
+      </c>
+      <c r="J8" s="49">
+        <v>0.08</v>
+      </c>
+      <c r="K8" s="62">
+        <v>0.08</v>
       </c>
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="71">
+      <c r="A9" s="70">
         <f t="shared" si="1"/>
-        <v>38738</v>
-      </c>
-      <c r="B9" s="62">
+        <v>46313</v>
+      </c>
+      <c r="B9" s="61">
         <f t="shared" si="2"/>
-        <v>38732</v>
-      </c>
-      <c r="C9" s="74">
+        <v>46307</v>
+      </c>
+      <c r="C9" s="73">
         <f t="shared" si="0"/>
-        <v>38738</v>
-      </c>
-      <c r="D9" s="77">
-        <v>25</v>
+        <v>46313</v>
+      </c>
+      <c r="D9" s="76">
+        <v>15</v>
       </c>
       <c r="E9" s="22">
         <f t="shared" si="3"/>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F9" s="35">
         <f t="shared" si="4"/>
-        <v>0.22388059701492538</v>
-      </c>
-      <c r="G9" s="49">
-        <v>28</v>
+        <v>0.16279069767441862</v>
+      </c>
+      <c r="G9" s="48">
+        <v>10</v>
       </c>
       <c r="H9" s="22">
         <f t="shared" si="5"/>
-        <v>73</v>
-      </c>
-      <c r="I9" s="78">
+        <v>25</v>
+      </c>
+      <c r="I9" s="77">
         <f t="shared" si="6"/>
-        <v>0.21791044776119403</v>
-      </c>
-      <c r="J9" s="50">
-        <v>0.2</v>
-      </c>
-      <c r="K9" s="63">
-        <v>0.18</v>
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="J9" s="49">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="62">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="71">
+      <c r="A10" s="70">
         <f t="shared" si="1"/>
-        <v>38745</v>
-      </c>
-      <c r="B10" s="62">
+        <v>46320</v>
+      </c>
+      <c r="B10" s="61">
         <f t="shared" si="2"/>
-        <v>38739</v>
-      </c>
-      <c r="C10" s="74">
+        <v>46314</v>
+      </c>
+      <c r="C10" s="73">
         <f t="shared" si="0"/>
-        <v>38745</v>
-      </c>
-      <c r="D10" s="77">
-        <v>25</v>
+        <v>46320</v>
+      </c>
+      <c r="D10" s="76">
+        <v>15</v>
       </c>
       <c r="E10" s="22">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F10" s="35">
         <f t="shared" si="4"/>
-        <v>0.29850746268656714</v>
-      </c>
-      <c r="G10" s="49">
-        <v>27</v>
-      </c>
+        <v>0.23255813953488372</v>
+      </c>
+      <c r="G10" s="48"/>
       <c r="H10" s="22">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="I10" s="78">
+        <v>25</v>
+      </c>
+      <c r="I10" s="77">
         <f t="shared" si="6"/>
-        <v>0.29850746268656714</v>
-      </c>
-      <c r="J10" s="50">
+        <v>0</v>
+      </c>
+      <c r="J10" s="49">
         <v>0.3</v>
       </c>
-      <c r="K10" s="63">
-        <v>0.31</v>
-      </c>
+      <c r="K10" s="62"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="71">
+      <c r="A11" s="70">
         <f t="shared" si="1"/>
-        <v>38752</v>
-      </c>
-      <c r="B11" s="62">
+        <v>46327</v>
+      </c>
+      <c r="B11" s="61">
         <f t="shared" si="2"/>
-        <v>38746</v>
-      </c>
-      <c r="C11" s="74">
+        <v>46321</v>
+      </c>
+      <c r="C11" s="73">
         <f t="shared" si="0"/>
-        <v>38752</v>
-      </c>
-      <c r="D11" s="77">
-        <v>25</v>
+        <v>46327</v>
+      </c>
+      <c r="D11" s="76">
+        <v>18</v>
       </c>
       <c r="E11" s="22">
         <f t="shared" si="3"/>
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="F11" s="35">
         <f t="shared" si="4"/>
-        <v>0.37313432835820898</v>
-      </c>
-      <c r="G11" s="49">
-        <v>20</v>
-      </c>
+        <v>0.31627906976744186</v>
+      </c>
+      <c r="G11" s="48"/>
       <c r="H11" s="22">
         <f t="shared" si="5"/>
-        <v>120</v>
-      </c>
-      <c r="I11" s="78">
+        <v>25</v>
+      </c>
+      <c r="I11" s="77">
         <f t="shared" si="6"/>
-        <v>0.35820895522388058</v>
-      </c>
-      <c r="J11" s="50">
+        <v>0</v>
+      </c>
+      <c r="J11" s="49">
         <v>0.4</v>
       </c>
-      <c r="K11" s="63">
-        <v>0.42</v>
-      </c>
+      <c r="K11" s="62"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="71">
+      <c r="A12" s="70">
         <f t="shared" si="1"/>
-        <v>38759</v>
-      </c>
-      <c r="B12" s="62">
+        <v>46334</v>
+      </c>
+      <c r="B12" s="61">
         <f t="shared" si="2"/>
-        <v>38753</v>
-      </c>
-      <c r="C12" s="74">
+        <v>46328</v>
+      </c>
+      <c r="C12" s="73">
         <f t="shared" si="0"/>
-        <v>38759</v>
-      </c>
-      <c r="D12" s="77">
-        <v>30</v>
+        <v>46334</v>
+      </c>
+      <c r="D12" s="76">
+        <v>18</v>
       </c>
       <c r="E12" s="22">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="F12" s="35">
         <f t="shared" si="4"/>
-        <v>0.46268656716417911</v>
-      </c>
-      <c r="G12" s="49">
-        <v>4</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="G12" s="48"/>
       <c r="H12" s="22">
         <f t="shared" si="5"/>
-        <v>124</v>
-      </c>
-      <c r="I12" s="78">
+        <v>25</v>
+      </c>
+      <c r="I12" s="77">
         <f t="shared" si="6"/>
-        <v>0.37014925373134328</v>
-      </c>
-      <c r="J12" s="50">
+        <v>0</v>
+      </c>
+      <c r="J12" s="49">
         <v>0.5</v>
       </c>
-      <c r="K12" s="63">
-        <v>0.48</v>
-      </c>
+      <c r="K12" s="62"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="71">
+      <c r="A13" s="70">
         <f t="shared" si="1"/>
-        <v>38766</v>
-      </c>
-      <c r="B13" s="62">
+        <v>46341</v>
+      </c>
+      <c r="B13" s="61">
         <f t="shared" si="2"/>
-        <v>38760</v>
-      </c>
-      <c r="C13" s="74">
+        <v>46335</v>
+      </c>
+      <c r="C13" s="73">
         <f t="shared" si="0"/>
-        <v>38766</v>
-      </c>
-      <c r="D13" s="77">
-        <v>30</v>
+        <v>46341</v>
+      </c>
+      <c r="D13" s="76">
+        <v>18</v>
       </c>
       <c r="E13" s="22">
         <f t="shared" si="3"/>
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="F13" s="35">
         <f t="shared" si="4"/>
-        <v>0.55223880597014929</v>
-      </c>
-      <c r="G13" s="49">
-        <v>30</v>
-      </c>
+        <v>0.48372093023255813</v>
+      </c>
+      <c r="G13" s="48"/>
       <c r="H13" s="22">
         <f t="shared" si="5"/>
-        <v>154</v>
-      </c>
-      <c r="I13" s="78">
+        <v>25</v>
+      </c>
+      <c r="I13" s="77">
         <f t="shared" si="6"/>
-        <v>0.45970149253731341</v>
-      </c>
-      <c r="J13" s="50">
+        <v>0</v>
+      </c>
+      <c r="J13" s="49">
         <v>0.6</v>
       </c>
-      <c r="K13" s="63">
-        <v>0.52</v>
-      </c>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="71">
+      <c r="A14" s="70">
         <f t="shared" si="1"/>
-        <v>38773</v>
-      </c>
-      <c r="B14" s="62">
+        <v>46348</v>
+      </c>
+      <c r="B14" s="61">
         <f t="shared" si="2"/>
-        <v>38767</v>
-      </c>
-      <c r="C14" s="74">
+        <v>46342</v>
+      </c>
+      <c r="C14" s="73">
         <f t="shared" si="0"/>
-        <v>38773</v>
-      </c>
-      <c r="D14" s="77">
-        <v>30</v>
+        <v>46348</v>
+      </c>
+      <c r="D14" s="76">
+        <v>18</v>
       </c>
       <c r="E14" s="22">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>122</v>
       </c>
       <c r="F14" s="35">
         <f t="shared" si="4"/>
-        <v>0.64179104477611937</v>
-      </c>
-      <c r="G14" s="49">
-        <v>40</v>
-      </c>
+        <v>0.56744186046511624</v>
+      </c>
+      <c r="G14" s="48"/>
       <c r="H14" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I14" s="78">
+        <v>25</v>
+      </c>
+      <c r="I14" s="77">
         <f t="shared" si="6"/>
-        <v>0.57910447761194028</v>
-      </c>
-      <c r="J14" s="50">
-        <v>0.65</v>
-      </c>
-      <c r="K14" s="63">
-        <v>0.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J14" s="49">
+        <v>0.7</v>
+      </c>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="71">
+      <c r="A15" s="70">
         <f t="shared" si="1"/>
-        <v>38780</v>
-      </c>
-      <c r="B15" s="62">
+        <v>46355</v>
+      </c>
+      <c r="B15" s="61">
         <f t="shared" si="2"/>
-        <v>38774</v>
-      </c>
-      <c r="C15" s="74">
+        <v>46349</v>
+      </c>
+      <c r="C15" s="73">
         <f t="shared" si="0"/>
-        <v>38780</v>
-      </c>
-      <c r="D15" s="77">
-        <v>30</v>
+        <v>46355</v>
+      </c>
+      <c r="D15" s="76">
+        <v>18</v>
       </c>
       <c r="E15" s="22">
         <f t="shared" si="3"/>
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="F15" s="35">
         <f t="shared" si="4"/>
-        <v>0.73134328358208955</v>
-      </c>
-      <c r="G15" s="49"/>
+        <v>0.65116279069767447</v>
+      </c>
+      <c r="G15" s="48"/>
       <c r="H15" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I15" s="78">
+        <v>25</v>
+      </c>
+      <c r="I15" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J15" s="50">
-        <v>0.7</v>
-      </c>
-      <c r="K15" s="63"/>
+      <c r="J15" s="49">
+        <v>0.8</v>
+      </c>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="71">
+      <c r="A16" s="70">
         <f t="shared" si="1"/>
-        <v>38787</v>
-      </c>
-      <c r="B16" s="62">
+        <v>46362</v>
+      </c>
+      <c r="B16" s="61">
         <f t="shared" si="2"/>
-        <v>38781</v>
-      </c>
-      <c r="C16" s="74">
+        <v>46356</v>
+      </c>
+      <c r="C16" s="73">
         <f t="shared" si="0"/>
-        <v>38787</v>
-      </c>
-      <c r="D16" s="77">
-        <v>30</v>
+        <v>46362</v>
+      </c>
+      <c r="D16" s="76">
+        <v>25</v>
       </c>
       <c r="E16" s="22">
         <f t="shared" si="3"/>
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="F16" s="35">
         <f t="shared" si="4"/>
-        <v>0.82089552238805974</v>
-      </c>
-      <c r="G16" s="49"/>
+        <v>0.76744186046511631</v>
+      </c>
+      <c r="G16" s="48"/>
       <c r="H16" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I16" s="78">
+        <v>25</v>
+      </c>
+      <c r="I16" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J16" s="50">
-        <v>0.8</v>
-      </c>
-      <c r="K16" s="63"/>
+      <c r="J16" s="49">
+        <v>0.9</v>
+      </c>
+      <c r="K16" s="62"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="71">
+      <c r="A17" s="70">
         <f t="shared" si="1"/>
-        <v>38794</v>
-      </c>
-      <c r="B17" s="62">
+        <v>46369</v>
+      </c>
+      <c r="B17" s="61">
         <f t="shared" si="2"/>
-        <v>38788</v>
-      </c>
-      <c r="C17" s="74">
+        <v>46363</v>
+      </c>
+      <c r="C17" s="73">
         <f t="shared" si="0"/>
-        <v>38794</v>
-      </c>
-      <c r="D17" s="77">
-        <v>30</v>
+        <v>46369</v>
+      </c>
+      <c r="D17" s="76">
+        <v>25</v>
       </c>
       <c r="E17" s="22">
         <f t="shared" si="3"/>
-        <v>305</v>
+        <v>190</v>
       </c>
       <c r="F17" s="35">
         <f t="shared" si="4"/>
-        <v>0.91044776119402981</v>
-      </c>
-      <c r="G17" s="49"/>
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="G17" s="48"/>
       <c r="H17" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I17" s="78">
+        <v>25</v>
+      </c>
+      <c r="I17" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J17" s="50">
-        <v>0.9</v>
-      </c>
-      <c r="K17" s="63"/>
+      <c r="J17" s="49">
+        <v>1</v>
+      </c>
+      <c r="K17" s="62"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="71">
+      <c r="A18" s="70">
         <f t="shared" si="1"/>
-        <v>38801</v>
-      </c>
-      <c r="B18" s="62">
+        <v>46376</v>
+      </c>
+      <c r="B18" s="61">
         <f t="shared" si="2"/>
-        <v>38795</v>
-      </c>
-      <c r="C18" s="74">
+        <v>46370</v>
+      </c>
+      <c r="C18" s="73">
         <f t="shared" si="0"/>
-        <v>38801</v>
-      </c>
-      <c r="D18" s="77">
-        <v>30</v>
+        <v>46376</v>
+      </c>
+      <c r="D18" s="76">
+        <v>25</v>
       </c>
       <c r="E18" s="22">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>215</v>
       </c>
       <c r="F18" s="35">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G18" s="49"/>
+      <c r="G18" s="48"/>
       <c r="H18" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I18" s="78">
+        <v>25</v>
+      </c>
+      <c r="I18" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J18" s="50">
+      <c r="J18" s="49">
         <v>1</v>
       </c>
-      <c r="K18" s="63"/>
+      <c r="K18" s="62"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="71">
+      <c r="A19" s="70">
         <f t="shared" si="1"/>
-        <v>38808</v>
-      </c>
-      <c r="B19" s="62">
+        <v>46383</v>
+      </c>
+      <c r="B19" s="61">
         <f>C18+1</f>
-        <v>38802</v>
-      </c>
-      <c r="C19" s="74">
+        <v>46377</v>
+      </c>
+      <c r="C19" s="73">
         <f>A19</f>
-        <v>38808</v>
-      </c>
-      <c r="D19" s="77"/>
+        <v>46383</v>
+      </c>
+      <c r="D19" s="76"/>
       <c r="E19" s="22">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>215</v>
       </c>
       <c r="F19" s="35">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G19" s="49"/>
+      <c r="G19" s="48"/>
       <c r="H19" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I19" s="78">
+        <v>25</v>
+      </c>
+      <c r="I19" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="63"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="62"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="71">
+      <c r="A20" s="70">
         <f t="shared" si="1"/>
-        <v>38815</v>
-      </c>
-      <c r="B20" s="62">
+        <v>46390</v>
+      </c>
+      <c r="B20" s="61">
         <f>C19+1</f>
-        <v>38809</v>
-      </c>
-      <c r="C20" s="74">
+        <v>46384</v>
+      </c>
+      <c r="C20" s="73">
         <f>A20</f>
-        <v>38815</v>
-      </c>
-      <c r="D20" s="77"/>
+        <v>46390</v>
+      </c>
+      <c r="D20" s="76"/>
       <c r="E20" s="22">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>215</v>
       </c>
       <c r="F20" s="35">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G20" s="49"/>
+      <c r="G20" s="48"/>
       <c r="H20" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I20" s="78">
+        <v>25</v>
+      </c>
+      <c r="I20" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J20" s="50"/>
-      <c r="K20" s="63"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="62"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="71">
+      <c r="A21" s="70">
         <f t="shared" si="1"/>
-        <v>38822</v>
-      </c>
-      <c r="B21" s="62">
+        <v>46397</v>
+      </c>
+      <c r="B21" s="61">
         <f>C20+1</f>
-        <v>38816</v>
-      </c>
-      <c r="C21" s="74">
+        <v>46391</v>
+      </c>
+      <c r="C21" s="73">
         <f>A21</f>
-        <v>38822</v>
-      </c>
-      <c r="D21" s="77"/>
+        <v>46397</v>
+      </c>
+      <c r="D21" s="76"/>
       <c r="E21" s="22">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>215</v>
       </c>
       <c r="F21" s="35">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G21" s="49"/>
+      <c r="G21" s="48"/>
       <c r="H21" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I21" s="78">
+        <v>25</v>
+      </c>
+      <c r="I21" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J21" s="50"/>
-      <c r="K21" s="63"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="62"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="71">
+      <c r="A22" s="70">
         <f t="shared" si="1"/>
-        <v>38829</v>
-      </c>
-      <c r="B22" s="62">
+        <v>46404</v>
+      </c>
+      <c r="B22" s="61">
         <f>C21+1</f>
-        <v>38823</v>
-      </c>
-      <c r="C22" s="74">
+        <v>46398</v>
+      </c>
+      <c r="C22" s="73">
         <f>A22</f>
-        <v>38829</v>
-      </c>
-      <c r="D22" s="77"/>
+        <v>46404</v>
+      </c>
+      <c r="D22" s="76"/>
       <c r="E22" s="22">
         <f t="shared" si="3"/>
-        <v>335</v>
+        <v>215</v>
       </c>
       <c r="F22" s="35">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G22" s="49"/>
+      <c r="G22" s="48"/>
       <c r="H22" s="22">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I22" s="78">
+        <v>25</v>
+      </c>
+      <c r="I22" s="77">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J22" s="50"/>
-      <c r="K22" s="63"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="62"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="72">
+      <c r="A23" s="71">
         <f t="shared" si="1"/>
-        <v>38836</v>
-      </c>
-      <c r="B23" s="64">
+        <v>46411</v>
+      </c>
+      <c r="B23" s="63">
         <f>C22+1</f>
-        <v>38830</v>
-      </c>
-      <c r="C23" s="75">
+        <v>46405</v>
+      </c>
+      <c r="C23" s="74">
         <f>A23</f>
-        <v>38836</v>
-      </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="65">
+        <v>46411</v>
+      </c>
+      <c r="D23" s="78"/>
+      <c r="E23" s="64">
         <f t="shared" si="3"/>
-        <v>335</v>
-      </c>
-      <c r="F23" s="66">
+        <v>215</v>
+      </c>
+      <c r="F23" s="65">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G23" s="67"/>
-      <c r="H23" s="65">
+      <c r="G23" s="66"/>
+      <c r="H23" s="64">
         <f t="shared" si="5"/>
-        <v>194</v>
-      </c>
-      <c r="I23" s="80">
+        <v>25</v>
+      </c>
+      <c r="I23" s="79">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J23" s="68"/>
-      <c r="K23" s="69"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="68"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" s="16"/>
@@ -12276,14 +11863,14 @@
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D25" s="45"/>
+      <c r="D25" s="44"/>
       <c r="E25" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25"/>
-      <c r="G25" s="46"/>
+      <c r="G25" s="45"/>
       <c r="H25" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -12309,7 +11896,7 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.47" right="0.45" top="0.49" bottom="0.37" header="0.37" footer="0.3"/>
-  <pageSetup paperSize="9" scale="58" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="64" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">

--- a/berichte/Report v3_1.xlsx
+++ b/berichte/Report v3_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oniku\IdeaProjects\SPM_MoinMetrics\berichte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F69E9B3-ADC2-4D13-BB30-50336D16483A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B078141-25DB-47E9-A8B9-10B3BA6490CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,8 +27,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Prof. Dr. Gerrit Jan Veltink - Persönliche Ansicht" guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1633" windowHeight="796" activeSheetId="2"/>
     <customWorkbookView name="Gert Veltink - Persönliche Ansicht" guid="{5EA89B68-426F-4FEF-AE0E-44F40F832319}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1176" windowHeight="713" activeSheetId="1"/>
-    <customWorkbookView name="Prof. Dr. Gerrit Jan Veltink - Persönliche Ansicht" guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" mergeInterval="0" personalView="1" maximized="1" windowWidth="1633" windowHeight="796" activeSheetId="2"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="90">
   <si>
     <t>: im 1. Bericht (Planung) eintragen</t>
   </si>
@@ -295,9 +295,6 @@
     <t>alexander.borrmann@stud.hs-emden-leer.de</t>
   </si>
   <si>
-    <t>Anforderungsanalyse und Aufwandseinschätzung</t>
-  </si>
-  <si>
     <t>MoinMetrics</t>
   </si>
   <si>
@@ -322,7 +319,10 @@
     <t>Abschluss Software-Architektur</t>
   </si>
   <si>
-    <t xml:space="preserve">Anforderungen wurden definiert. </t>
+    <t>Offene Abstimmungspunkte mit KaufDort abstimmen. Architektur und Systementwurf aus Anforderungen ableiten</t>
+  </si>
+  <si>
+    <t>Im Rahmen der Anforderungsanalyse wurden die Anforderungen der KaufDort-Warenkorbanalyse vollständig strukturiert und mit eindeutigen Bezeichnern versehen. Ergänzend wurden die Eigenschaften gut formulierter Anforderungen dokumentiert und offene Abstimmungspunkte je Anforderung festgehalten. Für die Aufwandsschätzung wurden zwei Verfahren durchgeführt: Die PERT-Expertenschätzung ergab einen Mittelwert von 220 Personenstunden. Die Analogieschätzung nach McConnell lieferte 291 Personenstunden. Daraus wurde ein Gesamtaufwand von 256 Personenstunden und ein Planungswert von 282 Personenstunden inklusive 10 % Risikoreserve abgeleitet. Das Vorgehen wurde in das V-Modell eingeordnet</t>
   </si>
 </sst>
 </file>
@@ -844,7 +844,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1154,29 +1154,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1261,8 +1240,33 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1680,7 +1684,7 @@
                   <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.19767441860465115</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2247,7 +2251,7 @@
                   <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.19767441860465115</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2882,6 +2886,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -2901,10 +2908,10 @@
                   <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46317</c:v>
+                  <c:v>46319</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>46319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3013,6 +3020,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3144,6 +3154,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3275,6 +3288,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3406,6 +3422,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3537,6 +3556,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -3667,6 +3689,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46411</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4215,6 +4240,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4234,10 +4262,10 @@
                   <c:v>46327</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46317</c:v>
+                  <c:v>46319</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>46319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4346,6 +4374,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4477,6 +4508,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4608,6 +4642,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4739,6 +4776,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -4870,6 +4910,9 @@
                 <c:pt idx="17">
                   <c:v>46411</c:v>
                 </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -5000,6 +5043,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>46411</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5656,7 +5702,7 @@
                   <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.19767441860465115</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -6788,6 +6834,9 @@
                 <c:pt idx="3">
                   <c:v>10</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6951,46 +7000,46 @@
                   <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>25</c:v>
+                  <c:v>42.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8136,7 +8185,7 @@
                   <c:v>0.11627906976744186</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.19767441860465115</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -9161,15 +9210,15 @@
       <c r="A2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="146" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
+      <c r="B2" s="139" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
       <c r="J2" s="123"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9197,7 +9246,7 @@
       </c>
       <c r="H3" s="95">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="J3" s="123" t="s">
         <v>63</v>
@@ -9245,11 +9294,11 @@
       <c r="A6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="148" t="s">
+      <c r="B6" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
+      <c r="C6" s="142"/>
+      <c r="D6" s="142"/>
       <c r="E6" s="118" t="s">
         <v>77</v>
       </c>
@@ -9264,11 +9313,11 @@
       <c r="A7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="142" t="s">
+      <c r="B7" s="135" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="143"/>
-      <c r="D7" s="143"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
       <c r="E7" s="118" t="s">
         <v>78</v>
       </c>
@@ -9283,11 +9332,11 @@
       <c r="A8" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="135" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="143"/>
-      <c r="D8" s="143"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="136"/>
       <c r="E8" s="118" t="s">
         <v>79</v>
       </c>
@@ -9302,11 +9351,11 @@
       <c r="A9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="144" t="s">
+      <c r="B9" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="145"/>
-      <c r="D9" s="145"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
       <c r="E9" s="87" t="s">
         <v>27</v>
       </c>
@@ -9336,11 +9385,11 @@
       <c r="A11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="150" t="s">
+      <c r="B11" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="151"/>
-      <c r="D11" s="151"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
       <c r="E11" s="118" t="s">
         <v>57</v>
       </c>
@@ -9355,11 +9404,11 @@
       <c r="A12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="152" t="s">
+      <c r="B12" s="145" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="146"/>
       <c r="E12" s="124"/>
       <c r="F12" s="99"/>
       <c r="G12" s="99"/>
@@ -9398,15 +9447,15 @@
       <c r="A15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="133" t="s">
+      <c r="B15" s="155" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="134"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="134"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="135"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="128"/>
       <c r="I15"/>
       <c r="J15" s="123" t="s">
         <v>67</v>
@@ -9414,109 +9463,109 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="136"/>
-      <c r="C16" s="137"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="137"/>
-      <c r="F16" s="137"/>
-      <c r="G16" s="137"/>
-      <c r="H16" s="138"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="131"/>
       <c r="I16"/>
       <c r="J16" s="123"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="137"/>
-      <c r="H17" s="138"/>
+      <c r="B17" s="129"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="131"/>
       <c r="I17"/>
       <c r="J17" s="123"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="136"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="137"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="137"/>
-      <c r="G18" s="137"/>
-      <c r="H18" s="138"/>
+      <c r="B18" s="129"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="131"/>
       <c r="I18"/>
       <c r="J18" s="123"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="136"/>
-      <c r="C19" s="137"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="137"/>
-      <c r="H19" s="138"/>
+      <c r="B19" s="129"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="131"/>
       <c r="I19"/>
       <c r="J19" s="123"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="136"/>
-      <c r="C20" s="137"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="137"/>
-      <c r="H20" s="138"/>
+      <c r="B20" s="129"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="130"/>
+      <c r="H20" s="131"/>
       <c r="I20"/>
       <c r="J20" s="123"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="136"/>
-      <c r="C21" s="137"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="138"/>
+      <c r="B21" s="129"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="131"/>
       <c r="I21"/>
       <c r="J21" s="123"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="136"/>
-      <c r="C22" s="137"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="138"/>
+      <c r="B22" s="129"/>
+      <c r="C22" s="130"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="130"/>
+      <c r="H22" s="131"/>
       <c r="I22"/>
       <c r="J22" s="123"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="136"/>
-      <c r="C23" s="137"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="137"/>
-      <c r="H23" s="138"/>
+      <c r="B23" s="129"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="131"/>
       <c r="I23"/>
       <c r="J23" s="123"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="139"/>
-      <c r="C24" s="140"/>
-      <c r="D24" s="140"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="140"/>
-      <c r="G24" s="140"/>
-      <c r="H24" s="141"/>
+      <c r="B24" s="132"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="134"/>
       <c r="I24"/>
       <c r="J24" s="123"/>
     </row>
@@ -9536,75 +9585,75 @@
       <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="133" t="s">
+      <c r="B26" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="134"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="135"/>
+      <c r="C26" s="127"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="127"/>
+      <c r="F26" s="127"/>
+      <c r="G26" s="127"/>
+      <c r="H26" s="128"/>
       <c r="I26"/>
       <c r="J26" s="123"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="136"/>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="138"/>
+      <c r="B27" s="129"/>
+      <c r="C27" s="130"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="130"/>
+      <c r="G27" s="130"/>
+      <c r="H27" s="131"/>
       <c r="I27"/>
       <c r="J27" s="123"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
-      <c r="B28" s="136"/>
-      <c r="C28" s="137"/>
-      <c r="D28" s="137"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
-      <c r="G28" s="137"/>
-      <c r="H28" s="138"/>
+      <c r="B28" s="129"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="131"/>
       <c r="I28"/>
       <c r="J28" s="123"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="136"/>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="138"/>
+      <c r="B29" s="129"/>
+      <c r="C29" s="130"/>
+      <c r="D29" s="130"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="130"/>
+      <c r="H29" s="131"/>
       <c r="I29"/>
       <c r="J29" s="123"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="136"/>
-      <c r="C30" s="137"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="137"/>
-      <c r="F30" s="137"/>
-      <c r="G30" s="137"/>
-      <c r="H30" s="138"/>
+      <c r="B30" s="129"/>
+      <c r="C30" s="130"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="131"/>
       <c r="I30"/>
       <c r="J30" s="123"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="139"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="141"/>
+      <c r="B31" s="132"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="133"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="133"/>
+      <c r="G31" s="133"/>
+      <c r="H31" s="134"/>
       <c r="I31"/>
       <c r="J31" s="123"/>
     </row>
@@ -9624,51 +9673,51 @@
       <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="133" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="134"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="134"/>
-      <c r="F33" s="134"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="135"/>
+      <c r="B33" s="126" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="127"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="127"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="128"/>
       <c r="I33"/>
       <c r="J33" s="123"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="136"/>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
-      <c r="H34" s="138"/>
+      <c r="B34" s="129"/>
+      <c r="C34" s="130"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="130"/>
+      <c r="H34" s="131"/>
       <c r="I34"/>
       <c r="J34" s="123"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
-      <c r="B35" s="136"/>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="138"/>
+      <c r="B35" s="129"/>
+      <c r="C35" s="130"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="130"/>
+      <c r="H35" s="131"/>
       <c r="I35"/>
       <c r="J35" s="123"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
-      <c r="B36" s="139"/>
-      <c r="C36" s="140"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="140"/>
-      <c r="F36" s="140"/>
-      <c r="G36" s="140"/>
-      <c r="H36" s="141"/>
+      <c r="B36" s="132"/>
+      <c r="C36" s="133"/>
+      <c r="D36" s="133"/>
+      <c r="E36" s="133"/>
+      <c r="F36" s="133"/>
+      <c r="G36" s="133"/>
+      <c r="H36" s="134"/>
       <c r="I36"/>
       <c r="J36" s="123"/>
     </row>
@@ -9688,75 +9737,75 @@
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="133" t="s">
+      <c r="B38" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="134"/>
-      <c r="D38" s="134"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="134"/>
-      <c r="G38" s="134"/>
-      <c r="H38" s="135"/>
+      <c r="C38" s="127"/>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="128"/>
       <c r="I38"/>
       <c r="J38" s="123"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="33"/>
-      <c r="B39" s="136"/>
-      <c r="C39" s="137"/>
-      <c r="D39" s="137"/>
-      <c r="E39" s="137"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="138"/>
+      <c r="B39" s="129"/>
+      <c r="C39" s="130"/>
+      <c r="D39" s="130"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="130"/>
+      <c r="H39" s="131"/>
       <c r="I39"/>
       <c r="J39" s="123"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="33"/>
-      <c r="B40" s="136"/>
-      <c r="C40" s="137"/>
-      <c r="D40" s="137"/>
-      <c r="E40" s="137"/>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
-      <c r="H40" s="138"/>
+      <c r="B40" s="129"/>
+      <c r="C40" s="130"/>
+      <c r="D40" s="130"/>
+      <c r="E40" s="130"/>
+      <c r="F40" s="130"/>
+      <c r="G40" s="130"/>
+      <c r="H40" s="131"/>
       <c r="I40"/>
       <c r="J40" s="123"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="33"/>
-      <c r="B41" s="136"/>
-      <c r="C41" s="137"/>
-      <c r="D41" s="137"/>
-      <c r="E41" s="137"/>
-      <c r="F41" s="137"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="138"/>
+      <c r="B41" s="129"/>
+      <c r="C41" s="130"/>
+      <c r="D41" s="130"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="130"/>
+      <c r="G41" s="130"/>
+      <c r="H41" s="131"/>
       <c r="I41"/>
       <c r="J41" s="123"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="33"/>
-      <c r="B42" s="136"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="138"/>
+      <c r="B42" s="129"/>
+      <c r="C42" s="130"/>
+      <c r="D42" s="130"/>
+      <c r="E42" s="130"/>
+      <c r="F42" s="130"/>
+      <c r="G42" s="130"/>
+      <c r="H42" s="131"/>
       <c r="I42"/>
       <c r="J42" s="123"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="33"/>
-      <c r="B43" s="139"/>
-      <c r="C43" s="140"/>
-      <c r="D43" s="140"/>
-      <c r="E43" s="140"/>
-      <c r="F43" s="140"/>
-      <c r="G43" s="140"/>
-      <c r="H43" s="141"/>
+      <c r="B43" s="132"/>
+      <c r="C43" s="133"/>
+      <c r="D43" s="133"/>
+      <c r="E43" s="133"/>
+      <c r="F43" s="133"/>
+      <c r="G43" s="133"/>
+      <c r="H43" s="134"/>
       <c r="I43"/>
       <c r="J43" s="123"/>
     </row>
@@ -10043,15 +10092,15 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67"/>
-      <c r="B67" s="147" t="s">
+      <c r="B67" s="140" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="147"/>
-      <c r="D67" s="147"/>
-      <c r="E67" s="147"/>
-      <c r="F67" s="147"/>
-      <c r="G67" s="147"/>
-      <c r="H67" s="147"/>
+      <c r="C67" s="140"/>
+      <c r="D67" s="140"/>
+      <c r="E67" s="140"/>
+      <c r="F67" s="140"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="140"/>
       <c r="I67"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -10078,15 +10127,15 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{5EA89B68-426F-4FEF-AE0E-44F40F832319}" fitToPage="1" showRuler="0">
-      <selection activeCell="F6" sqref="F6"/>
+    <customSheetView guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" fitToPage="1" showRuler="0" topLeftCell="A25">
+      <selection activeCell="L7" sqref="L7"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <headerFooter>
         <oddHeader>&amp;C&amp;"Arial,Fett"&amp;12- Projektbericht -</oddHeader>
       </headerFooter>
     </customSheetView>
-    <customSheetView guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" fitToPage="1" showRuler="0" topLeftCell="A25">
-      <selection activeCell="L7" sqref="L7"/>
+    <customSheetView guid="{5EA89B68-426F-4FEF-AE0E-44F40F832319}" fitToPage="1" showRuler="0">
+      <selection activeCell="F6" sqref="F6"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <headerFooter>
         <oddHeader>&amp;C&amp;"Arial,Fett"&amp;12- Projektbericht -</oddHeader>
@@ -10115,11 +10164,11 @@
     <hyperlink ref="E8" r:id="rId4" xr:uid="{2C84892D-1520-4847-8F81-E6960892FAC2}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.51181102362204722" bottom="0.19685039370078741" header="0.23622047244094491" footer="0.27559055118110237"/>
-  <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="88" orientation="portrait" r:id="rId5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Arial,Fett"&amp;12- Projektbericht -</oddHeader>
   </headerFooter>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
@@ -10184,28 +10233,28 @@
       </c>
       <c r="B4" s="108"/>
       <c r="C4" s="102" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="103" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="103" t="s">
+      <c r="F4" s="103" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="103" t="s">
+      <c r="G4" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="103" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="103" t="s">
+      <c r="H4" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="104" t="s">
+      <c r="I4" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="105" t="s">
-        <v>86</v>
-      </c>
       <c r="J4" s="39"/>
-      <c r="K4" s="154"/>
+      <c r="K4" s="125"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
@@ -10349,7 +10398,7 @@
         <v>46313</v>
       </c>
       <c r="C8" s="41">
-        <v>46317</v>
+        <v>46319</v>
       </c>
       <c r="D8" s="41">
         <v>46334</v>
@@ -10833,10 +10882,15 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="42"/>
+      <c r="A25" s="42">
+        <v>46319</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
       <c r="C25" s="40">
         <f>A25</f>
-        <v>0</v>
+        <v>46319</v>
       </c>
       <c r="D25" s="40"/>
       <c r="E25" s="40"/>
@@ -11044,12 +11098,12 @@
     </row>
   </sheetData>
   <customSheetViews>
+    <customSheetView guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview" showRuler="0">
+      <selection activeCell="E27" sqref="E27"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
     <customSheetView guid="{5EA89B68-426F-4FEF-AE0E-44F40F832319}" fitToPage="1" showRuler="0">
       <selection activeCell="B26" sqref="B26"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview" showRuler="0">
-      <selection activeCell="E27" sqref="E27"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
   </customSheetViews>
@@ -11122,31 +11176,31 @@
       <c r="A4" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="131" t="s">
+      <c r="B4" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="127" t="s">
+      <c r="C4" s="154"/>
+      <c r="D4" s="149" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
       <c r="I4" s="47"/>
-      <c r="J4" s="129" t="s">
+      <c r="J4" s="151" t="s">
         <v>52</v>
       </c>
-      <c r="K4" s="130"/>
+      <c r="K4" s="152"/>
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="125" t="s">
+      <c r="B5" s="147" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="126"/>
+      <c r="C5" s="148"/>
       <c r="D5" s="51" t="s">
         <v>45</v>
       </c>
@@ -11363,14 +11417,16 @@
         <f t="shared" si="4"/>
         <v>0.23255813953488372</v>
       </c>
-      <c r="G10" s="48"/>
+      <c r="G10" s="48">
+        <v>17.5</v>
+      </c>
       <c r="H10" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I10" s="77">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.19767441860465115</v>
       </c>
       <c r="J10" s="49">
         <v>0.3</v>
@@ -11404,7 +11460,7 @@
       <c r="G11" s="48"/>
       <c r="H11" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I11" s="77">
         <f t="shared" si="6"/>
@@ -11442,7 +11498,7 @@
       <c r="G12" s="48"/>
       <c r="H12" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I12" s="77">
         <f t="shared" si="6"/>
@@ -11480,7 +11536,7 @@
       <c r="G13" s="48"/>
       <c r="H13" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I13" s="77">
         <f t="shared" si="6"/>
@@ -11518,7 +11574,7 @@
       <c r="G14" s="48"/>
       <c r="H14" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I14" s="77">
         <f t="shared" si="6"/>
@@ -11556,7 +11612,7 @@
       <c r="G15" s="48"/>
       <c r="H15" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I15" s="77">
         <f t="shared" si="6"/>
@@ -11594,7 +11650,7 @@
       <c r="G16" s="48"/>
       <c r="H16" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I16" s="77">
         <f t="shared" si="6"/>
@@ -11632,7 +11688,7 @@
       <c r="G17" s="48"/>
       <c r="H17" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I17" s="77">
         <f t="shared" si="6"/>
@@ -11670,7 +11726,7 @@
       <c r="G18" s="48"/>
       <c r="H18" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I18" s="77">
         <f t="shared" si="6"/>
@@ -11706,7 +11762,7 @@
       <c r="G19" s="48"/>
       <c r="H19" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I19" s="77">
         <f t="shared" si="6"/>
@@ -11740,7 +11796,7 @@
       <c r="G20" s="48"/>
       <c r="H20" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I20" s="77">
         <f t="shared" si="6"/>
@@ -11774,7 +11830,7 @@
       <c r="G21" s="48"/>
       <c r="H21" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I21" s="77">
         <f t="shared" si="6"/>
@@ -11808,7 +11864,7 @@
       <c r="G22" s="48"/>
       <c r="H22" s="22">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I22" s="77">
         <f t="shared" si="6"/>
@@ -11842,7 +11898,7 @@
       <c r="G23" s="66"/>
       <c r="H23" s="64">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="I23" s="79">
         <f t="shared" si="6"/>
@@ -11879,12 +11935,12 @@
     </row>
   </sheetData>
   <customSheetViews>
+    <customSheetView guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview" showRuler="0" topLeftCell="A10">
+      <selection activeCell="D18" sqref="D18"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+    </customSheetView>
     <customSheetView guid="{5EA89B68-426F-4FEF-AE0E-44F40F832319}" fitToPage="1" showRuler="0">
       <selection activeCell="C14" sqref="C14"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-    </customSheetView>
-    <customSheetView guid="{267CC0B3-6A13-40E2-B883-F5101A181CE5}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" view="pageBreakPreview" showRuler="0" topLeftCell="A10">
-      <selection activeCell="D18" sqref="D18"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
     </customSheetView>
   </customSheetViews>
